--- a/Elin_JustDoomIt/LangMod/JP/Thing.xlsx
+++ b/Elin_JustDoomIt/LangMod/JP/Thing.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="70">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -233,6 +233,9 @@
   </si>
   <si>
     <t xml:space="preserve">obj</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eternity</t>
   </si>
   <si>
     <t xml:space="preserve">SlotMachine</t>
@@ -494,7 +497,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="7.14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="11.45"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="11.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="7.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="7.55"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="0" width="8.95"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="5.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="0" width="3.51"/>
@@ -902,8 +905,11 @@
       <c r="N4" s="0" t="n">
         <v>3033</v>
       </c>
+      <c r="Y4" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="AA4" s="0" t="n">
-        <v>14000</v>
+        <v>45000</v>
       </c>
       <c r="AF4" s="0" t="n">
         <v>120000</v>
@@ -912,13 +918,13 @@
         <v>-10</v>
       </c>
       <c r="AH4" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AY4" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AZ4" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/Elin_JustDoomIt/LangMod/JP/Thing.xlsx
+++ b/Elin_JustDoomIt/LangMod/JP/Thing.xlsx
@@ -238,7 +238,7 @@
     <t xml:space="preserve">eternity</t>
   </si>
   <si>
-    <t xml:space="preserve">SlotMachine</t>
+    <t xml:space="preserve">JustDoomArcade</t>
   </si>
   <si>
     <r>
@@ -506,6 +506,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="31" min="31" style="0" width="3.51"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="32" min="32" style="0" width="6.72"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="33" min="33" style="0" width="9.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="34" min="34" style="0" width="15.49"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="35" min="35" style="0" width="8.95"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="36" min="36" style="0" width="6.02"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="37" min="37" style="0" width="10.61"/>

--- a/Elin_JustDoomIt/LangMod/JP/Thing.xlsx
+++ b/Elin_JustDoomIt/LangMod/JP/Thing.xlsx
@@ -232,7 +232,7 @@
     <t xml:space="preserve">ObjBig</t>
   </si>
   <si>
-    <t xml:space="preserve">obj</t>
+    <t xml:space="preserve">@obj</t>
   </si>
   <si>
     <t xml:space="preserve">eternity</t>
